--- a/artfynd/A 38910-2023 artfynd.xlsx
+++ b/artfynd/A 38910-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131199554</v>
       </c>
       <c r="B2" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38910-2023 artfynd.xlsx
+++ b/artfynd/A 38910-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131199554</v>
       </c>
       <c r="B2" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38910-2023 artfynd.xlsx
+++ b/artfynd/A 38910-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131199554</v>
       </c>
       <c r="B2" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38910-2023 artfynd.xlsx
+++ b/artfynd/A 38910-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131199554</v>
       </c>
       <c r="B2" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38910-2023 artfynd.xlsx
+++ b/artfynd/A 38910-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>132251077</v>
       </c>
       <c r="B3" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38910-2023 artfynd.xlsx
+++ b/artfynd/A 38910-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>132251077</v>
       </c>
       <c r="B3" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38910-2023 artfynd.xlsx
+++ b/artfynd/A 38910-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -906,6 +906,127 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134179450</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99095</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Anderstorp N, Anderstorp N, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>467707</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6544746</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38910-2023 artfynd.xlsx
+++ b/artfynd/A 38910-2023 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>134179450</v>
       </c>
       <c r="B4" t="n">
-        <v>99095</v>
+        <v>99097</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38910-2023 artfynd.xlsx
+++ b/artfynd/A 38910-2023 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>134179450</v>
       </c>
       <c r="B4" t="n">
-        <v>99098</v>
+        <v>99105</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38910-2023 artfynd.xlsx
+++ b/artfynd/A 38910-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131199554</v>
       </c>
       <c r="B2" t="n">
-        <v>57086</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>132251077</v>
       </c>
       <c r="B3" t="n">
-        <v>57142</v>
+        <v>57162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>134179450</v>
       </c>
       <c r="B4" t="n">
-        <v>99105</v>
+        <v>99112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38910-2023 artfynd.xlsx
+++ b/artfynd/A 38910-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131199554</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132251077</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,8 +1041,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134179450</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>